--- a/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10815</v>
+        <v>0.0893</v>
       </c>
       <c r="E2">
-        <v>0.1813</v>
+        <v>0.15445</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>147.5</v>
+        <v>109.2</v>
       </c>
       <c r="L2">
-        <v>0.4099499722067815</v>
+        <v>0.3473282442748091</v>
       </c>
       <c r="M2">
-        <v>48.49</v>
+        <v>95.25</v>
       </c>
       <c r="N2">
-        <v>0.03071125467097346</v>
+        <v>0.06874774449657163</v>
       </c>
       <c r="O2">
-        <v>0.3287457627118644</v>
+        <v>0.8722527472527474</v>
       </c>
       <c r="P2">
-        <v>47.16</v>
+        <v>93.19999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02986889606688201</v>
+        <v>0.06726813424756405</v>
       </c>
       <c r="R2">
-        <v>0.319728813559322</v>
+        <v>0.8534798534798534</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>2.050000000000001</v>
       </c>
       <c r="T2">
-        <v>0.0274283357393277</v>
+        <v>0.0215223097112861</v>
       </c>
       <c r="U2">
-        <v>281.5</v>
+        <v>530.1</v>
       </c>
       <c r="V2">
-        <v>0.1782886819937931</v>
+        <v>0.3826055575604475</v>
       </c>
       <c r="W2">
-        <v>0.138494180000451</v>
+        <v>0.09170611158761699</v>
       </c>
       <c r="X2">
-        <v>0.1310533828624492</v>
+        <v>0.1415027744286365</v>
       </c>
       <c r="Y2">
-        <v>0.007440797138001831</v>
+        <v>-0.04979666284101947</v>
       </c>
       <c r="Z2">
-        <v>0.05727110658347129</v>
+        <v>0.04540400028882952</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04799742042500702</v>
+        <v>0.06678633511895318</v>
       </c>
       <c r="AC2">
-        <v>-0.04799742042500702</v>
+        <v>-0.06678633511895318</v>
       </c>
       <c r="AD2">
-        <v>5884.200000000001</v>
+        <v>5724.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5884.200000000001</v>
+        <v>5724.5</v>
       </c>
       <c r="AG2">
-        <v>5602.700000000001</v>
+        <v>5194.4</v>
       </c>
       <c r="AH2">
-        <v>0.7884391204727259</v>
+        <v>0.8051336146272855</v>
       </c>
       <c r="AI2">
-        <v>0.8165015402547665</v>
+        <v>0.8494205629664802</v>
       </c>
       <c r="AJ2">
-        <v>0.7801464854628496</v>
+        <v>0.7894344898858645</v>
       </c>
       <c r="AK2">
-        <v>0.8090424687008131</v>
+        <v>0.8365650969529086</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07730000000000001</v>
+        <v>0.0126</v>
       </c>
       <c r="E3">
-        <v>0.0516</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>76.8</v>
+        <v>55.9</v>
       </c>
       <c r="L3">
-        <v>0.3243243243243243</v>
+        <v>0.306469298245614</v>
       </c>
       <c r="M3">
-        <v>42.7</v>
+        <v>69.8</v>
       </c>
       <c r="N3">
-        <v>0.04275130156187425</v>
+        <v>0.08856744068011672</v>
       </c>
       <c r="O3">
-        <v>0.5559895833333334</v>
+        <v>1.24865831842576</v>
       </c>
       <c r="P3">
-        <v>42.7</v>
+        <v>69.8</v>
       </c>
       <c r="Q3">
-        <v>0.04275130156187425</v>
+        <v>0.08856744068011672</v>
       </c>
       <c r="R3">
-        <v>0.5559895833333334</v>
+        <v>1.24865831842576</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>44.2</v>
+        <v>175.9</v>
       </c>
       <c r="V3">
-        <v>0.04425310372446937</v>
+        <v>0.2231950260119274</v>
       </c>
       <c r="W3">
-        <v>0.1012925349512002</v>
+        <v>0.06379821958456973</v>
       </c>
       <c r="X3">
-        <v>0.1338006388270918</v>
+        <v>0.1425569762472856</v>
       </c>
       <c r="Y3">
-        <v>-0.03250810387589158</v>
+        <v>-0.07875875666271588</v>
       </c>
       <c r="Z3">
-        <v>0.05285596303653937</v>
+        <v>0.03930780337478181</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04766411130105584</v>
+        <v>0.06618537335092081</v>
       </c>
       <c r="AC3">
-        <v>-0.04766411130105584</v>
+        <v>-0.06618537335092081</v>
       </c>
       <c r="AD3">
-        <v>3808.3</v>
+        <v>3293.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3808.3</v>
+        <v>3293.7</v>
       </c>
       <c r="AG3">
-        <v>3764.1</v>
+        <v>3117.8</v>
       </c>
       <c r="AH3">
-        <v>0.792224001997046</v>
+        <v>0.8069234161399382</v>
       </c>
       <c r="AI3">
-        <v>0.8129576262141104</v>
+        <v>0.8307773798113303</v>
       </c>
       <c r="AJ3">
-        <v>0.790295828171912</v>
+        <v>0.7982283212575847</v>
       </c>
       <c r="AK3">
-        <v>0.8111760015516238</v>
+        <v>0.8229207907725605</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.139</v>
+        <v>0.166</v>
       </c>
       <c r="E4">
-        <v>0.311</v>
+        <v>0.222</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>70.7</v>
+        <v>53.3</v>
       </c>
       <c r="L4">
-        <v>0.5747967479674797</v>
+        <v>0.4037878787878788</v>
       </c>
       <c r="M4">
-        <v>5.79</v>
+        <v>25.45</v>
       </c>
       <c r="N4">
-        <v>0.009981037752111704</v>
+        <v>0.04260127217944426</v>
       </c>
       <c r="O4">
-        <v>0.08189533239038189</v>
+        <v>0.4774859287054409</v>
       </c>
       <c r="P4">
-        <v>4.46</v>
+        <v>23.4</v>
       </c>
       <c r="Q4">
-        <v>0.007688329598345113</v>
+        <v>0.03916973552058922</v>
       </c>
       <c r="R4">
-        <v>0.06308345120226308</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>2.050000000000001</v>
       </c>
       <c r="T4">
-        <v>0.229706390328152</v>
+        <v>0.08055009823182714</v>
       </c>
       <c r="U4">
-        <v>237.3</v>
+        <v>354.2</v>
       </c>
       <c r="V4">
-        <v>0.4090674021720393</v>
+        <v>0.5929025778372949</v>
       </c>
       <c r="W4">
-        <v>0.1756958250497018</v>
+        <v>0.1196140035906643</v>
       </c>
       <c r="X4">
-        <v>0.1283061268978065</v>
+        <v>0.1404485726099873</v>
       </c>
       <c r="Y4">
-        <v>0.04738969815189525</v>
+        <v>-0.02083456901932301</v>
       </c>
       <c r="Z4">
-        <v>0.06824612994507018</v>
+        <v>0.05778828473863935</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0483307295489582</v>
+        <v>0.06738729688698557</v>
       </c>
       <c r="AC4">
-        <v>-0.0483307295489582</v>
+        <v>-0.06738729688698557</v>
       </c>
       <c r="AD4">
-        <v>2075.9</v>
+        <v>2430.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2075.9</v>
+        <v>2430.8</v>
       </c>
       <c r="AG4">
-        <v>1838.6</v>
+        <v>2076.6</v>
       </c>
       <c r="AH4">
-        <v>0.7815888554216868</v>
+        <v>0.8027210884353742</v>
       </c>
       <c r="AI4">
-        <v>0.8230839379881845</v>
+        <v>0.8760586730096948</v>
       </c>
       <c r="AJ4">
-        <v>0.7601604167528011</v>
+        <v>0.7765893792071803</v>
       </c>
       <c r="AK4">
-        <v>0.8047093837535014</v>
+        <v>0.8579219169593059</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0893</v>
+        <v>0.09404999999999999</v>
       </c>
       <c r="E2">
-        <v>0.15445</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>109.2</v>
+        <v>126.6</v>
       </c>
       <c r="L2">
-        <v>0.3473282442748091</v>
+        <v>0.3297733784839802</v>
       </c>
       <c r="M2">
-        <v>95.25</v>
+        <v>49.4</v>
       </c>
       <c r="N2">
-        <v>0.06874774449657163</v>
+        <v>0.03225174642554025</v>
       </c>
       <c r="O2">
-        <v>0.8722527472527474</v>
+        <v>0.3902053712480253</v>
       </c>
       <c r="P2">
-        <v>93.19999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="Q2">
-        <v>0.06726813424756405</v>
+        <v>0.03225174642554025</v>
       </c>
       <c r="R2">
-        <v>0.8534798534798534</v>
+        <v>0.3902053712480253</v>
       </c>
       <c r="S2">
-        <v>2.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0215223097112861</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>530.1</v>
+        <v>530.6</v>
       </c>
       <c r="V2">
-        <v>0.3826055575604475</v>
+        <v>0.3464124828621793</v>
       </c>
       <c r="W2">
-        <v>0.09170611158761699</v>
+        <v>0.1671994206373708</v>
       </c>
       <c r="X2">
-        <v>0.1415027744286365</v>
+        <v>0.1086360636240449</v>
       </c>
       <c r="Y2">
-        <v>-0.04979666284101947</v>
+        <v>0.05856335701332592</v>
       </c>
       <c r="Z2">
-        <v>0.04540400028882952</v>
+        <v>0.06182761064227275</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06678633511895318</v>
+        <v>0.05628638331911779</v>
       </c>
       <c r="AC2">
-        <v>-0.06678633511895318</v>
+        <v>-0.05628638331911779</v>
       </c>
       <c r="AD2">
-        <v>5724.5</v>
+        <v>6876.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5724.5</v>
+        <v>6876.4</v>
       </c>
       <c r="AG2">
-        <v>5194.4</v>
+        <v>6345.799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.8051336146272855</v>
+        <v>0.8178304254231038</v>
       </c>
       <c r="AI2">
-        <v>0.8494205629664802</v>
+        <v>0.8454520864583077</v>
       </c>
       <c r="AJ2">
-        <v>0.7894344898858645</v>
+        <v>0.80556013963821</v>
       </c>
       <c r="AK2">
-        <v>0.8365650969529086</v>
+        <v>0.8346661756195086</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0126</v>
+        <v>-0.0319</v>
       </c>
       <c r="E3">
-        <v>0.08689999999999999</v>
+        <v>-0.172</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>55.9</v>
+        <v>23.8</v>
       </c>
       <c r="L3">
-        <v>0.306469298245614</v>
+        <v>0.1441550575408843</v>
       </c>
       <c r="M3">
-        <v>69.8</v>
+        <v>35.4</v>
       </c>
       <c r="N3">
-        <v>0.08856744068011672</v>
+        <v>0.04690605538624618</v>
       </c>
       <c r="O3">
-        <v>1.24865831842576</v>
+        <v>1.487394957983193</v>
       </c>
       <c r="P3">
-        <v>69.8</v>
+        <v>35.4</v>
       </c>
       <c r="Q3">
-        <v>0.08856744068011672</v>
+        <v>0.04690605538624618</v>
       </c>
       <c r="R3">
-        <v>1.24865831842576</v>
+        <v>1.487394957983193</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>175.9</v>
+        <v>145.9</v>
       </c>
       <c r="V3">
-        <v>0.2231950260119274</v>
+        <v>0.1933218497416192</v>
       </c>
       <c r="W3">
-        <v>0.06379821958456973</v>
+        <v>0.03547473543001938</v>
       </c>
       <c r="X3">
-        <v>0.1425569762472856</v>
+        <v>0.1199724641418105</v>
       </c>
       <c r="Y3">
-        <v>-0.07875875666271588</v>
+        <v>-0.08449772871179115</v>
       </c>
       <c r="Z3">
-        <v>0.03930780337478181</v>
+        <v>0.04357695251669438</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06618537335092081</v>
+        <v>0.05594361646838912</v>
       </c>
       <c r="AC3">
-        <v>-0.06618537335092081</v>
+        <v>-0.05594361646838912</v>
       </c>
       <c r="AD3">
-        <v>3293.7</v>
+        <v>4103.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3293.7</v>
+        <v>4103.2</v>
       </c>
       <c r="AG3">
-        <v>3117.8</v>
+        <v>3957.3</v>
       </c>
       <c r="AH3">
-        <v>0.8069234161399382</v>
+        <v>0.8446448053685749</v>
       </c>
       <c r="AI3">
-        <v>0.8307773798113303</v>
+        <v>0.8503336510962822</v>
       </c>
       <c r="AJ3">
-        <v>0.7982283212575847</v>
+        <v>0.8398344651952461</v>
       </c>
       <c r="AK3">
-        <v>0.8229207907725605</v>
+        <v>0.8456672721444598</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.166</v>
+        <v>0.22</v>
       </c>
       <c r="E4">
-        <v>0.222</v>
+        <v>0.316</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>53.3</v>
+        <v>102.8</v>
       </c>
       <c r="L4">
-        <v>0.4037878787878788</v>
+        <v>0.469835466179159</v>
       </c>
       <c r="M4">
-        <v>25.45</v>
+        <v>14</v>
       </c>
       <c r="N4">
-        <v>0.04260127217944426</v>
+        <v>0.01801801801801802</v>
       </c>
       <c r="O4">
-        <v>0.4774859287054409</v>
+        <v>0.1361867704280156</v>
       </c>
       <c r="P4">
-        <v>23.4</v>
+        <v>14</v>
       </c>
       <c r="Q4">
-        <v>0.03916973552058922</v>
+        <v>0.01801801801801802</v>
       </c>
       <c r="R4">
-        <v>0.4390243902439024</v>
+        <v>0.1361867704280156</v>
       </c>
       <c r="S4">
-        <v>2.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.08055009823182714</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>354.2</v>
+        <v>384.7</v>
       </c>
       <c r="V4">
-        <v>0.5929025778372949</v>
+        <v>0.4951093951093951</v>
       </c>
       <c r="W4">
-        <v>0.1196140035906643</v>
+        <v>0.2989241058447223</v>
       </c>
       <c r="X4">
-        <v>0.1404485726099873</v>
+        <v>0.09729966310627931</v>
       </c>
       <c r="Y4">
-        <v>-0.02083456901932301</v>
+        <v>0.201624442738443</v>
       </c>
       <c r="Z4">
-        <v>0.05778828473863935</v>
+        <v>0.09039454658128485</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06738729688698557</v>
+        <v>0.05662915016984646</v>
       </c>
       <c r="AC4">
-        <v>-0.06738729688698557</v>
+        <v>-0.05662915016984646</v>
       </c>
       <c r="AD4">
-        <v>2430.8</v>
+        <v>2773.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2430.8</v>
+        <v>2773.2</v>
       </c>
       <c r="AG4">
-        <v>2076.6</v>
+        <v>2388.5</v>
       </c>
       <c r="AH4">
-        <v>0.8027210884353742</v>
+        <v>0.7811390907554504</v>
       </c>
       <c r="AI4">
-        <v>0.8760586730096948</v>
+        <v>0.8383313180169286</v>
       </c>
       <c r="AJ4">
-        <v>0.7765893792071803</v>
+        <v>0.754541146738272</v>
       </c>
       <c r="AK4">
-        <v>0.8579219169593059</v>
+        <v>0.8170560667738515</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09404999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="E2">
-        <v>0.07200000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>126.6</v>
+        <v>188</v>
       </c>
       <c r="L2">
-        <v>0.3297733784839802</v>
+        <v>0.3468634686346864</v>
       </c>
       <c r="M2">
-        <v>49.4</v>
+        <v>93.69</v>
       </c>
       <c r="N2">
-        <v>0.03225174642554025</v>
+        <v>0.08847860987817545</v>
       </c>
       <c r="O2">
-        <v>0.3902053712480253</v>
+        <v>0.4983510638297872</v>
       </c>
       <c r="P2">
-        <v>49.4</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03225174642554025</v>
+        <v>0.08631598828973462</v>
       </c>
       <c r="R2">
-        <v>0.3902053712480253</v>
+        <v>0.4861702127659575</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.289999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02444230974490339</v>
       </c>
       <c r="U2">
-        <v>530.6</v>
+        <v>791.1</v>
       </c>
       <c r="V2">
-        <v>0.3464124828621793</v>
+        <v>0.7470960430635565</v>
       </c>
       <c r="W2">
-        <v>0.1671994206373708</v>
+        <v>0.1490563871673584</v>
       </c>
       <c r="X2">
-        <v>0.1086360636240449</v>
+        <v>0.1539819116080937</v>
       </c>
       <c r="Y2">
-        <v>0.05856335701332592</v>
+        <v>-0.004925524440735268</v>
       </c>
       <c r="Z2">
-        <v>0.06182761064227275</v>
+        <v>0.07133756620442029</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05628638331911779</v>
+        <v>0.05983966752380767</v>
       </c>
       <c r="AC2">
-        <v>-0.05628638331911779</v>
+        <v>-0.05983966752380767</v>
       </c>
       <c r="AD2">
-        <v>6876.4</v>
+        <v>8362.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6876.4</v>
+        <v>8362.6</v>
       </c>
       <c r="AG2">
-        <v>6345.799999999999</v>
+        <v>7571.5</v>
       </c>
       <c r="AH2">
-        <v>0.8178304254231038</v>
+        <v>0.8876081303401794</v>
       </c>
       <c r="AI2">
-        <v>0.8454520864583077</v>
+        <v>0.8523958535068853</v>
       </c>
       <c r="AJ2">
-        <v>0.80556013963821</v>
+        <v>0.8773058027437894</v>
       </c>
       <c r="AK2">
-        <v>0.8346661756195086</v>
+        <v>0.8394496429996895</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0319</v>
+        <v>0.108</v>
       </c>
       <c r="E3">
-        <v>-0.172</v>
+        <v>0.135</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>23.8</v>
+        <v>110.1</v>
       </c>
       <c r="L3">
-        <v>0.1441550575408843</v>
+        <v>0.3325279371791</v>
       </c>
       <c r="M3">
-        <v>35.4</v>
+        <v>59.3</v>
       </c>
       <c r="N3">
-        <v>0.04690605538624618</v>
+        <v>0.08529919447640966</v>
       </c>
       <c r="O3">
-        <v>1.487394957983193</v>
+        <v>0.5386012715712988</v>
       </c>
       <c r="P3">
-        <v>35.4</v>
+        <v>59.3</v>
       </c>
       <c r="Q3">
-        <v>0.04690605538624618</v>
+        <v>0.08529919447640966</v>
       </c>
       <c r="R3">
-        <v>1.487394957983193</v>
+        <v>0.5386012715712988</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>145.9</v>
+        <v>88.2</v>
       </c>
       <c r="V3">
-        <v>0.1933218497416192</v>
+        <v>0.1268699654775604</v>
       </c>
       <c r="W3">
-        <v>0.03547473543001938</v>
+        <v>0.1524508446413736</v>
       </c>
       <c r="X3">
-        <v>0.1199724641418105</v>
+        <v>0.1413370623709808</v>
       </c>
       <c r="Y3">
-        <v>-0.08449772871179115</v>
+        <v>0.01111378227039272</v>
       </c>
       <c r="Z3">
-        <v>0.04357695251669438</v>
+        <v>0.07075542258788332</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05594361646838912</v>
+        <v>0.05895260853392191</v>
       </c>
       <c r="AC3">
-        <v>-0.05594361646838912</v>
+        <v>-0.05895260853392191</v>
       </c>
       <c r="AD3">
-        <v>4103.2</v>
+        <v>4960.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4103.2</v>
+        <v>4960.3</v>
       </c>
       <c r="AG3">
-        <v>3957.3</v>
+        <v>4872.1</v>
       </c>
       <c r="AH3">
-        <v>0.8446448053685749</v>
+        <v>0.8770754133144727</v>
       </c>
       <c r="AI3">
-        <v>0.8503336510962822</v>
+        <v>0.8572786505590985</v>
       </c>
       <c r="AJ3">
-        <v>0.8398344651952461</v>
+        <v>0.8751279794514397</v>
       </c>
       <c r="AK3">
-        <v>0.8456672721444598</v>
+        <v>0.855069411537584</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.22</v>
+        <v>0.178</v>
       </c>
       <c r="E4">
-        <v>0.316</v>
+        <v>0.213</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>102.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L4">
-        <v>0.469835466179159</v>
+        <v>0.3693693693693694</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>34.39</v>
       </c>
       <c r="N4">
-        <v>0.01801801801801802</v>
+        <v>0.09455595270827606</v>
       </c>
       <c r="O4">
-        <v>0.1361867704280156</v>
+        <v>0.4414634146341463</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>32.1</v>
       </c>
       <c r="Q4">
-        <v>0.01801801801801802</v>
+        <v>0.08825955457794886</v>
       </c>
       <c r="R4">
-        <v>0.1361867704280156</v>
+        <v>0.4120667522464698</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.289999999999999</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.06658912474556554</v>
       </c>
       <c r="U4">
-        <v>384.7</v>
+        <v>702.9</v>
       </c>
       <c r="V4">
-        <v>0.4951093951093951</v>
+        <v>1.932636788562002</v>
       </c>
       <c r="W4">
-        <v>0.2989241058447223</v>
+        <v>0.1456619296933433</v>
       </c>
       <c r="X4">
-        <v>0.09729966310627931</v>
+        <v>0.1666267608452066</v>
       </c>
       <c r="Y4">
-        <v>0.201624442738443</v>
+        <v>-0.02096483115186323</v>
       </c>
       <c r="Z4">
-        <v>0.09039454658128485</v>
+        <v>0.07227107306608914</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05662915016984646</v>
+        <v>0.06072672651369343</v>
       </c>
       <c r="AC4">
-        <v>-0.05662915016984646</v>
+        <v>-0.06072672651369343</v>
       </c>
       <c r="AD4">
-        <v>2773.2</v>
+        <v>3402.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2773.2</v>
+        <v>3402.3</v>
       </c>
       <c r="AG4">
-        <v>2388.5</v>
+        <v>2699.4</v>
       </c>
       <c r="AH4">
-        <v>0.7811390907554504</v>
+        <v>0.9034253850238981</v>
       </c>
       <c r="AI4">
-        <v>0.8383313180169286</v>
+        <v>0.8453759379814143</v>
       </c>
       <c r="AJ4">
-        <v>0.754541146738272</v>
+        <v>0.881264078874343</v>
       </c>
       <c r="AK4">
-        <v>0.8170560667738515</v>
+        <v>0.8126561700334167</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_banks_regional.xlsx
@@ -645,10 +645,10 @@
         <v>0.1490563871673584</v>
       </c>
       <c r="X2">
-        <v>0.1539819116080937</v>
+        <v>0.1539257416593584</v>
       </c>
       <c r="Y2">
-        <v>-0.004925524440735268</v>
+        <v>-0.004869354491999961</v>
       </c>
       <c r="Z2">
         <v>0.07133756620442029</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05983966752380767</v>
+        <v>0.0598335893937741</v>
       </c>
       <c r="AC2">
-        <v>-0.05983966752380767</v>
+        <v>-0.0598335893937741</v>
       </c>
       <c r="AD2">
         <v>8362.6</v>
@@ -767,10 +767,10 @@
         <v>0.1524508446413736</v>
       </c>
       <c r="X3">
-        <v>0.1413370623709808</v>
+        <v>0.1412874578500778</v>
       </c>
       <c r="Y3">
-        <v>0.01111378227039272</v>
+        <v>0.01116338679129578</v>
       </c>
       <c r="Z3">
         <v>0.07075542258788332</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05895260853392191</v>
+        <v>0.05894651091869217</v>
       </c>
       <c r="AC3">
-        <v>-0.05895260853392191</v>
+        <v>-0.05894651091869217</v>
       </c>
       <c r="AD3">
         <v>4960.3</v>
@@ -889,10 +889,10 @@
         <v>0.1456619296933433</v>
       </c>
       <c r="X4">
-        <v>0.1666267608452066</v>
+        <v>0.166564025468639</v>
       </c>
       <c r="Y4">
-        <v>-0.02096483115186323</v>
+        <v>-0.0209020957752957</v>
       </c>
       <c r="Z4">
         <v>0.07227107306608914</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06072672651369343</v>
+        <v>0.06072066786885603</v>
       </c>
       <c r="AC4">
-        <v>-0.06072672651369343</v>
+        <v>-0.06072066786885603</v>
       </c>
       <c r="AD4">
         <v>3402.3</v>
